--- a/IAST.xlsx
+++ b/IAST.xlsx
@@ -6613,7 +6613,7 @@
     <t>added 11.06.24</t>
   </si>
   <si>
-    <t>muni</t>
+    <t>muni(s)</t>
   </si>
   <si>
     <t>munimji</t>
@@ -9244,10 +9244,10 @@
     <t>samarpayami</t>
   </si>
   <si>
-    <t>Samarth Rāmadās</t>
-  </si>
-  <si>
-    <t>Samarth Ramadas</t>
+    <t>Samarth Rāmdās</t>
+  </si>
+  <si>
+    <t>Samarth Ramdas</t>
   </si>
   <si>
     <t>samatva-yoga</t>
@@ -45189,10 +45189,10 @@
       <c r="V1094" s="2"/>
     </row>
     <row r="1095" ht="12.75" customHeight="1">
-      <c r="A1095" s="7" t="s">
+      <c r="A1095" s="16" t="s">
         <v>2123</v>
       </c>
-      <c r="B1095" s="7" t="s">
+      <c r="B1095" s="16" t="s">
         <v>2123</v>
       </c>
       <c r="C1095" s="2"/>

--- a/IAST.xlsx
+++ b/IAST.xlsx
@@ -27,14 +27,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="kXd/6d5C1oqeuwf1kNbGKM1OTRvIJCUXnszVo1AdlYE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="86PBZ5KA/xMN3UDovYrHGLmdp1rhAmVAl2pq2vv25Co="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4702" uniqueCount="4179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4712" uniqueCount="4187">
   <si>
     <t>IAST</t>
   </si>
@@ -4308,7 +4308,7 @@
     <t>Janmashtami</t>
   </si>
   <si>
-    <t>japa</t>
+    <t>japa(m)</t>
   </si>
   <si>
     <t>Japa Walk</t>
@@ -5262,16 +5262,16 @@
     <t>Krishna-arpan</t>
   </si>
   <si>
-    <t>Kṛṣṇa-arpaṇam</t>
-  </si>
-  <si>
-    <t>Krishna-arpanam</t>
-  </si>
-  <si>
-    <t>Kṛṣṇa-arpaṇam astu</t>
-  </si>
-  <si>
-    <t>Krishna-arpanam astu</t>
+    <t>Kṛṣṇārpaṇam</t>
+  </si>
+  <si>
+    <t>Krishnarpanam</t>
+  </si>
+  <si>
+    <t>Kṛṣṇārpaṇam astu</t>
+  </si>
+  <si>
+    <t>Krishnarpanam astu</t>
   </si>
   <si>
     <t>split into 2 01.08.23</t>
@@ -12942,6 +12942,30 @@
   </si>
   <si>
     <t>Bhakti-devi</t>
+  </si>
+  <si>
+    <t>parama-prema-rūpā</t>
+  </si>
+  <si>
+    <t>parama-prema-rupa</t>
+  </si>
+  <si>
+    <t>Maitreyī</t>
+  </si>
+  <si>
+    <t>Maitreyi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raghunātha </t>
+  </si>
+  <si>
+    <t>Raghunatha</t>
+  </si>
+  <si>
+    <t>bhoga-japa(m)</t>
+  </si>
+  <si>
+    <t>Satyanārāyaṇa Kathā</t>
   </si>
   <si>
     <t>EVENT NAMES</t>
@@ -34162,10 +34186,10 @@
       <c r="V707" s="2"/>
     </row>
     <row r="708" ht="12.75" customHeight="1">
-      <c r="A708" s="7" t="s">
+      <c r="A708" s="16" t="s">
         <v>1368</v>
       </c>
-      <c r="B708" s="4" t="s">
+      <c r="B708" s="3" t="s">
         <v>1368</v>
       </c>
       <c r="C708" s="2"/>
@@ -38778,10 +38802,10 @@
       <c r="V870" s="2"/>
     </row>
     <row r="871" ht="12.75" customHeight="1">
-      <c r="A871" s="7" t="s">
+      <c r="A871" s="16" t="s">
         <v>1686</v>
       </c>
-      <c r="B871" s="7" t="s">
+      <c r="B871" s="16" t="s">
         <v>1687</v>
       </c>
       <c r="C871" s="2"/>
@@ -74230,8 +74254,12 @@
       <c r="V2120" s="2"/>
     </row>
     <row r="2121" ht="12.75" customHeight="1">
-      <c r="A2121" s="45"/>
-      <c r="B2121" s="45"/>
+      <c r="A2121" s="3" t="s">
+        <v>4102</v>
+      </c>
+      <c r="B2121" s="3" t="s">
+        <v>4103</v>
+      </c>
       <c r="C2121" s="2"/>
       <c r="D2121" s="2"/>
       <c r="E2121" s="2"/>
@@ -74254,8 +74282,12 @@
       <c r="V2121" s="2"/>
     </row>
     <row r="2122" ht="12.75" customHeight="1">
-      <c r="A2122" s="45"/>
-      <c r="B2122" s="45"/>
+      <c r="A2122" s="70" t="s">
+        <v>4104</v>
+      </c>
+      <c r="B2122" s="70" t="s">
+        <v>4105</v>
+      </c>
       <c r="C2122" s="2"/>
       <c r="D2122" s="2"/>
       <c r="E2122" s="2"/>
@@ -74276,6 +74308,258 @@
       <c r="T2122" s="2"/>
       <c r="U2122" s="2"/>
       <c r="V2122" s="2"/>
+    </row>
+    <row r="2123" ht="12.75" customHeight="1">
+      <c r="A2123" s="70" t="s">
+        <v>4106</v>
+      </c>
+      <c r="B2123" s="70" t="s">
+        <v>4107</v>
+      </c>
+      <c r="C2123" s="2"/>
+      <c r="D2123" s="2"/>
+      <c r="E2123" s="2"/>
+      <c r="F2123" s="2"/>
+      <c r="G2123" s="2"/>
+      <c r="H2123" s="2"/>
+      <c r="I2123" s="2"/>
+      <c r="J2123" s="2"/>
+      <c r="K2123" s="2"/>
+      <c r="L2123" s="2"/>
+      <c r="M2123" s="2"/>
+      <c r="N2123" s="2"/>
+      <c r="O2123" s="2"/>
+      <c r="P2123" s="2"/>
+      <c r="Q2123" s="2"/>
+      <c r="R2123" s="2"/>
+      <c r="S2123" s="2"/>
+      <c r="T2123" s="2"/>
+      <c r="U2123" s="2"/>
+      <c r="V2123" s="2"/>
+    </row>
+    <row r="2124" ht="12.75" customHeight="1">
+      <c r="A2124" s="3" t="s">
+        <v>4108</v>
+      </c>
+      <c r="B2124" s="3" t="s">
+        <v>4108</v>
+      </c>
+      <c r="C2124" s="2"/>
+      <c r="D2124" s="2"/>
+      <c r="E2124" s="2"/>
+      <c r="F2124" s="2"/>
+      <c r="G2124" s="2"/>
+      <c r="H2124" s="2"/>
+      <c r="I2124" s="2"/>
+      <c r="J2124" s="2"/>
+      <c r="K2124" s="2"/>
+      <c r="L2124" s="2"/>
+      <c r="M2124" s="2"/>
+      <c r="N2124" s="2"/>
+      <c r="O2124" s="2"/>
+      <c r="P2124" s="2"/>
+      <c r="Q2124" s="2"/>
+      <c r="R2124" s="2"/>
+      <c r="S2124" s="2"/>
+      <c r="T2124" s="2"/>
+      <c r="U2124" s="2"/>
+      <c r="V2124" s="2"/>
+    </row>
+    <row r="2125" ht="12.75" customHeight="1">
+      <c r="A2125" s="70" t="s">
+        <v>4109</v>
+      </c>
+      <c r="B2125" s="70" t="s">
+        <v>4109</v>
+      </c>
+      <c r="C2125" s="2"/>
+      <c r="D2125" s="2"/>
+      <c r="E2125" s="2"/>
+      <c r="F2125" s="2"/>
+      <c r="G2125" s="2"/>
+      <c r="H2125" s="2"/>
+      <c r="I2125" s="2"/>
+      <c r="J2125" s="2"/>
+      <c r="K2125" s="2"/>
+      <c r="L2125" s="2"/>
+      <c r="M2125" s="2"/>
+      <c r="N2125" s="2"/>
+      <c r="O2125" s="2"/>
+      <c r="P2125" s="2"/>
+      <c r="Q2125" s="2"/>
+      <c r="R2125" s="2"/>
+      <c r="S2125" s="2"/>
+      <c r="T2125" s="2"/>
+      <c r="U2125" s="2"/>
+      <c r="V2125" s="2"/>
+    </row>
+    <row r="2126" ht="12.75" customHeight="1">
+      <c r="A2126" s="45"/>
+      <c r="B2126" s="45"/>
+      <c r="C2126" s="2"/>
+      <c r="D2126" s="2"/>
+      <c r="E2126" s="2"/>
+      <c r="F2126" s="2"/>
+      <c r="G2126" s="2"/>
+      <c r="H2126" s="2"/>
+      <c r="I2126" s="2"/>
+      <c r="J2126" s="2"/>
+      <c r="K2126" s="2"/>
+      <c r="L2126" s="2"/>
+      <c r="M2126" s="2"/>
+      <c r="N2126" s="2"/>
+      <c r="O2126" s="2"/>
+      <c r="P2126" s="2"/>
+      <c r="Q2126" s="2"/>
+      <c r="R2126" s="2"/>
+      <c r="S2126" s="2"/>
+      <c r="T2126" s="2"/>
+      <c r="U2126" s="2"/>
+      <c r="V2126" s="2"/>
+    </row>
+    <row r="2127" ht="12.75" customHeight="1">
+      <c r="A2127" s="45"/>
+      <c r="B2127" s="45"/>
+      <c r="C2127" s="2"/>
+      <c r="D2127" s="2"/>
+      <c r="E2127" s="2"/>
+      <c r="F2127" s="2"/>
+      <c r="G2127" s="2"/>
+      <c r="H2127" s="2"/>
+      <c r="I2127" s="2"/>
+      <c r="J2127" s="2"/>
+      <c r="K2127" s="2"/>
+      <c r="L2127" s="2"/>
+      <c r="M2127" s="2"/>
+      <c r="N2127" s="2"/>
+      <c r="O2127" s="2"/>
+      <c r="P2127" s="2"/>
+      <c r="Q2127" s="2"/>
+      <c r="R2127" s="2"/>
+      <c r="S2127" s="2"/>
+      <c r="T2127" s="2"/>
+      <c r="U2127" s="2"/>
+      <c r="V2127" s="2"/>
+    </row>
+    <row r="2128" ht="12.75" customHeight="1">
+      <c r="A2128" s="45"/>
+      <c r="B2128" s="45"/>
+      <c r="C2128" s="2"/>
+      <c r="D2128" s="2"/>
+      <c r="E2128" s="2"/>
+      <c r="F2128" s="2"/>
+      <c r="G2128" s="2"/>
+      <c r="H2128" s="2"/>
+      <c r="I2128" s="2"/>
+      <c r="J2128" s="2"/>
+      <c r="K2128" s="2"/>
+      <c r="L2128" s="2"/>
+      <c r="M2128" s="2"/>
+      <c r="N2128" s="2"/>
+      <c r="O2128" s="2"/>
+      <c r="P2128" s="2"/>
+      <c r="Q2128" s="2"/>
+      <c r="R2128" s="2"/>
+      <c r="S2128" s="2"/>
+      <c r="T2128" s="2"/>
+      <c r="U2128" s="2"/>
+      <c r="V2128" s="2"/>
+    </row>
+    <row r="2129" ht="12.75" customHeight="1">
+      <c r="A2129" s="45"/>
+      <c r="B2129" s="45"/>
+      <c r="C2129" s="2"/>
+      <c r="D2129" s="2"/>
+      <c r="E2129" s="2"/>
+      <c r="F2129" s="2"/>
+      <c r="G2129" s="2"/>
+      <c r="H2129" s="2"/>
+      <c r="I2129" s="2"/>
+      <c r="J2129" s="2"/>
+      <c r="K2129" s="2"/>
+      <c r="L2129" s="2"/>
+      <c r="M2129" s="2"/>
+      <c r="N2129" s="2"/>
+      <c r="O2129" s="2"/>
+      <c r="P2129" s="2"/>
+      <c r="Q2129" s="2"/>
+      <c r="R2129" s="2"/>
+      <c r="S2129" s="2"/>
+      <c r="T2129" s="2"/>
+      <c r="U2129" s="2"/>
+      <c r="V2129" s="2"/>
+    </row>
+    <row r="2130" ht="12.75" customHeight="1">
+      <c r="A2130" s="45"/>
+      <c r="B2130" s="45"/>
+      <c r="C2130" s="2"/>
+      <c r="D2130" s="2"/>
+      <c r="E2130" s="2"/>
+      <c r="F2130" s="2"/>
+      <c r="G2130" s="2"/>
+      <c r="H2130" s="2"/>
+      <c r="I2130" s="2"/>
+      <c r="J2130" s="2"/>
+      <c r="K2130" s="2"/>
+      <c r="L2130" s="2"/>
+      <c r="M2130" s="2"/>
+      <c r="N2130" s="2"/>
+      <c r="O2130" s="2"/>
+      <c r="P2130" s="2"/>
+      <c r="Q2130" s="2"/>
+      <c r="R2130" s="2"/>
+      <c r="S2130" s="2"/>
+      <c r="T2130" s="2"/>
+      <c r="U2130" s="2"/>
+      <c r="V2130" s="2"/>
+    </row>
+    <row r="2131" ht="12.75" customHeight="1">
+      <c r="A2131" s="45"/>
+      <c r="B2131" s="45"/>
+      <c r="C2131" s="2"/>
+      <c r="D2131" s="2"/>
+      <c r="E2131" s="2"/>
+      <c r="F2131" s="2"/>
+      <c r="G2131" s="2"/>
+      <c r="H2131" s="2"/>
+      <c r="I2131" s="2"/>
+      <c r="J2131" s="2"/>
+      <c r="K2131" s="2"/>
+      <c r="L2131" s="2"/>
+      <c r="M2131" s="2"/>
+      <c r="N2131" s="2"/>
+      <c r="O2131" s="2"/>
+      <c r="P2131" s="2"/>
+      <c r="Q2131" s="2"/>
+      <c r="R2131" s="2"/>
+      <c r="S2131" s="2"/>
+      <c r="T2131" s="2"/>
+      <c r="U2131" s="2"/>
+      <c r="V2131" s="2"/>
+    </row>
+    <row r="2132" ht="12.75" customHeight="1">
+      <c r="A2132" s="45"/>
+      <c r="B2132" s="45"/>
+      <c r="C2132" s="2"/>
+      <c r="D2132" s="2"/>
+      <c r="E2132" s="2"/>
+      <c r="F2132" s="2"/>
+      <c r="G2132" s="2"/>
+      <c r="H2132" s="2"/>
+      <c r="I2132" s="2"/>
+      <c r="J2132" s="2"/>
+      <c r="K2132" s="2"/>
+      <c r="L2132" s="2"/>
+      <c r="M2132" s="2"/>
+      <c r="N2132" s="2"/>
+      <c r="O2132" s="2"/>
+      <c r="P2132" s="2"/>
+      <c r="Q2132" s="2"/>
+      <c r="R2132" s="2"/>
+      <c r="S2132" s="2"/>
+      <c r="T2132" s="2"/>
+      <c r="U2132" s="2"/>
+      <c r="V2132" s="2"/>
     </row>
   </sheetData>
   <printOptions gridLines="1"/>
@@ -74298,7 +74582,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="161" t="s">
-        <v>4102</v>
+        <v>4110</v>
       </c>
       <c r="B1" s="162"/>
       <c r="C1" s="163"/>
@@ -74324,10 +74608,10 @@
     </row>
     <row r="2">
       <c r="A2" s="162" t="s">
-        <v>4103</v>
+        <v>4111</v>
       </c>
       <c r="B2" s="162" t="s">
-        <v>4104</v>
+        <v>4112</v>
       </c>
       <c r="C2" s="163"/>
       <c r="D2" s="163"/>
@@ -74352,10 +74636,10 @@
     </row>
     <row r="3">
       <c r="A3" s="164" t="s">
-        <v>4105</v>
+        <v>4113</v>
       </c>
       <c r="B3" s="165" t="s">
-        <v>4106</v>
+        <v>4114</v>
       </c>
       <c r="C3" s="163"/>
       <c r="D3" s="163"/>
@@ -74404,10 +74688,10 @@
     </row>
     <row r="5">
       <c r="A5" s="164" t="s">
-        <v>4107</v>
+        <v>4115</v>
       </c>
       <c r="B5" s="165" t="s">
-        <v>4108</v>
+        <v>4116</v>
       </c>
       <c r="C5" s="163"/>
       <c r="D5" s="163"/>
@@ -74456,10 +74740,10 @@
     </row>
     <row r="7">
       <c r="A7" s="164" t="s">
-        <v>4109</v>
+        <v>4117</v>
       </c>
       <c r="B7" s="165" t="s">
-        <v>4110</v>
+        <v>4118</v>
       </c>
       <c r="C7" s="163"/>
       <c r="D7" s="163"/>
@@ -74508,10 +74792,10 @@
     </row>
     <row r="9">
       <c r="A9" s="167" t="s">
-        <v>4111</v>
+        <v>4119</v>
       </c>
       <c r="B9" s="168" t="s">
-        <v>4112</v>
+        <v>4120</v>
       </c>
       <c r="C9" s="163"/>
       <c r="D9" s="163"/>
@@ -74560,7 +74844,7 @@
     </row>
     <row r="11">
       <c r="A11" s="164" t="s">
-        <v>4113</v>
+        <v>4121</v>
       </c>
       <c r="B11" s="165" t="s">
         <v>1840</v>
@@ -74612,10 +74896,10 @@
     </row>
     <row r="13">
       <c r="A13" s="169" t="s">
-        <v>4114</v>
+        <v>4122</v>
       </c>
       <c r="B13" s="165" t="s">
-        <v>4115</v>
+        <v>4123</v>
       </c>
       <c r="C13" s="163"/>
       <c r="D13" s="163"/>
@@ -74664,10 +74948,10 @@
     </row>
     <row r="15">
       <c r="A15" s="169" t="s">
-        <v>4116</v>
+        <v>4124</v>
       </c>
       <c r="B15" s="165" t="s">
-        <v>4117</v>
+        <v>4125</v>
       </c>
       <c r="C15" s="163"/>
       <c r="D15" s="163"/>
@@ -74716,10 +75000,10 @@
     </row>
     <row r="17">
       <c r="A17" s="169" t="s">
-        <v>4118</v>
+        <v>4126</v>
       </c>
       <c r="B17" s="165" t="s">
-        <v>4119</v>
+        <v>4127</v>
       </c>
       <c r="C17" s="163"/>
       <c r="D17" s="163"/>
@@ -74768,10 +75052,10 @@
     </row>
     <row r="19">
       <c r="A19" s="169" t="s">
-        <v>4120</v>
+        <v>4128</v>
       </c>
       <c r="B19" s="165" t="s">
-        <v>4121</v>
+        <v>4129</v>
       </c>
       <c r="C19" s="163"/>
       <c r="D19" s="163"/>
@@ -74820,10 +75104,10 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="169" t="s">
-        <v>4122</v>
+        <v>4130</v>
       </c>
       <c r="B21" s="165" t="s">
-        <v>4123</v>
+        <v>4131</v>
       </c>
       <c r="C21" s="163"/>
       <c r="D21" s="163"/>
@@ -74872,10 +75156,10 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="169" t="s">
-        <v>4124</v>
+        <v>4132</v>
       </c>
       <c r="B23" s="165" t="s">
-        <v>4125</v>
+        <v>4133</v>
       </c>
       <c r="C23" s="163"/>
       <c r="D23" s="163"/>
@@ -74924,10 +75208,10 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="169" t="s">
-        <v>4126</v>
+        <v>4134</v>
       </c>
       <c r="B25" s="165" t="s">
-        <v>4127</v>
+        <v>4135</v>
       </c>
       <c r="C25" s="163"/>
       <c r="D25" s="163"/>
@@ -74976,10 +75260,10 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="169" t="s">
-        <v>4128</v>
+        <v>4136</v>
       </c>
       <c r="B27" s="165" t="s">
-        <v>4129</v>
+        <v>4137</v>
       </c>
       <c r="C27" s="163"/>
       <c r="D27" s="163"/>
@@ -75028,10 +75312,10 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="169" t="s">
-        <v>4130</v>
+        <v>4138</v>
       </c>
       <c r="B29" s="165" t="s">
-        <v>4131</v>
+        <v>4139</v>
       </c>
       <c r="C29" s="163"/>
       <c r="D29" s="163"/>
@@ -75080,7 +75364,7 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="164" t="s">
-        <v>4132</v>
+        <v>4140</v>
       </c>
       <c r="B31" s="165" t="s">
         <v>1241</v>
@@ -75132,10 +75416,10 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="164" t="s">
-        <v>4133</v>
+        <v>4141</v>
       </c>
       <c r="B33" s="165" t="s">
-        <v>4134</v>
+        <v>4142</v>
       </c>
       <c r="C33" s="163"/>
       <c r="D33" s="163"/>
@@ -75184,7 +75468,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="164" t="s">
-        <v>4135</v>
+        <v>4143</v>
       </c>
       <c r="B35" s="165" t="s">
         <v>2205</v>
@@ -75236,7 +75520,7 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="164" t="s">
-        <v>4136</v>
+        <v>4144</v>
       </c>
       <c r="B37" s="165" t="s">
         <v>1854</v>
@@ -75288,10 +75572,10 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="164" t="s">
-        <v>4137</v>
+        <v>4145</v>
       </c>
       <c r="B39" s="165" t="s">
-        <v>4137</v>
+        <v>4145</v>
       </c>
       <c r="C39" s="163"/>
       <c r="D39" s="163"/>
@@ -75340,10 +75624,10 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="164" t="s">
-        <v>4138</v>
+        <v>4146</v>
       </c>
       <c r="B41" s="165" t="s">
-        <v>4138</v>
+        <v>4146</v>
       </c>
       <c r="C41" s="163"/>
       <c r="D41" s="163"/>
@@ -75392,10 +75676,10 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="164" t="s">
-        <v>4139</v>
+        <v>4147</v>
       </c>
       <c r="B43" s="165" t="s">
-        <v>4139</v>
+        <v>4147</v>
       </c>
       <c r="C43" s="163"/>
       <c r="D43" s="163"/>
@@ -75444,10 +75728,10 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="164" t="s">
-        <v>4140</v>
+        <v>4148</v>
       </c>
       <c r="B45" s="165" t="s">
-        <v>4140</v>
+        <v>4148</v>
       </c>
       <c r="C45" s="163"/>
       <c r="D45" s="163"/>
@@ -75496,10 +75780,10 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="169" t="s">
-        <v>4141</v>
+        <v>4149</v>
       </c>
       <c r="B47" s="165" t="s">
-        <v>4142</v>
+        <v>4150</v>
       </c>
       <c r="C47" s="163"/>
       <c r="D47" s="163"/>
@@ -75548,7 +75832,7 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="165" t="s">
-        <v>4143</v>
+        <v>4151</v>
       </c>
       <c r="B49" s="165" t="s">
         <v>2723</v>
@@ -75600,7 +75884,7 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="164" t="s">
-        <v>4144</v>
+        <v>4152</v>
       </c>
       <c r="B51" s="165" t="s">
         <v>1062</v>
@@ -75652,10 +75936,10 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="164" t="s">
-        <v>4145</v>
+        <v>4153</v>
       </c>
       <c r="B53" s="165" t="s">
-        <v>4146</v>
+        <v>4154</v>
       </c>
       <c r="C53" s="163"/>
       <c r="D53" s="163"/>
@@ -75704,10 +75988,10 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="165" t="s">
-        <v>4147</v>
+        <v>4155</v>
       </c>
       <c r="B55" s="165" t="s">
-        <v>4148</v>
+        <v>4156</v>
       </c>
       <c r="C55" s="163"/>
       <c r="D55" s="163"/>
@@ -75756,10 +76040,10 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="164" t="s">
-        <v>4149</v>
+        <v>4157</v>
       </c>
       <c r="B57" s="165" t="s">
-        <v>4150</v>
+        <v>4158</v>
       </c>
       <c r="C57" s="163"/>
       <c r="D57" s="163"/>
@@ -75808,10 +76092,10 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="169" t="s">
-        <v>4151</v>
+        <v>4159</v>
       </c>
       <c r="B59" s="165" t="s">
-        <v>4152</v>
+        <v>4160</v>
       </c>
       <c r="C59" s="163"/>
       <c r="D59" s="163"/>
@@ -75860,10 +76144,10 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="169" t="s">
-        <v>4153</v>
+        <v>4161</v>
       </c>
       <c r="B61" s="165" t="s">
-        <v>4154</v>
+        <v>4162</v>
       </c>
       <c r="C61" s="163"/>
       <c r="D61" s="163"/>
@@ -75912,10 +76196,10 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="169" t="s">
-        <v>4155</v>
+        <v>4163</v>
       </c>
       <c r="B63" s="165" t="s">
-        <v>4156</v>
+        <v>4164</v>
       </c>
       <c r="C63" s="163"/>
       <c r="D63" s="163"/>
@@ -75964,10 +76248,10 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="169" t="s">
-        <v>4157</v>
+        <v>4165</v>
       </c>
       <c r="B65" s="165" t="s">
-        <v>4158</v>
+        <v>4166</v>
       </c>
       <c r="C65" s="163"/>
       <c r="D65" s="163"/>
@@ -76016,10 +76300,10 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="169" t="s">
-        <v>4159</v>
+        <v>4167</v>
       </c>
       <c r="B67" s="165" t="s">
-        <v>4160</v>
+        <v>4168</v>
       </c>
       <c r="C67" s="163"/>
       <c r="D67" s="163"/>
@@ -76068,10 +76352,10 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="169" t="s">
-        <v>4161</v>
+        <v>4169</v>
       </c>
       <c r="B69" s="165" t="s">
-        <v>4162</v>
+        <v>4170</v>
       </c>
       <c r="C69" s="163"/>
       <c r="D69" s="163"/>
@@ -76120,10 +76404,10 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="169" t="s">
-        <v>4163</v>
+        <v>4171</v>
       </c>
       <c r="B71" s="165" t="s">
-        <v>4164</v>
+        <v>4172</v>
       </c>
       <c r="C71" s="163"/>
       <c r="D71" s="163"/>
@@ -76172,10 +76456,10 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="169" t="s">
-        <v>4165</v>
+        <v>4173</v>
       </c>
       <c r="B73" s="165" t="s">
-        <v>4166</v>
+        <v>4174</v>
       </c>
       <c r="C73" s="163"/>
       <c r="D73" s="163"/>
@@ -76224,10 +76508,10 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="165" t="s">
-        <v>4167</v>
+        <v>4175</v>
       </c>
       <c r="B75" s="171" t="s">
-        <v>4168</v>
+        <v>4176</v>
       </c>
       <c r="C75" s="163"/>
       <c r="D75" s="163"/>
@@ -76276,7 +76560,7 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="169" t="s">
-        <v>4169</v>
+        <v>4177</v>
       </c>
       <c r="B77" s="165" t="s">
         <v>856</v>
@@ -76328,10 +76612,10 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="165" t="s">
-        <v>4170</v>
+        <v>4178</v>
       </c>
       <c r="B79" s="171" t="s">
-        <v>4171</v>
+        <v>4179</v>
       </c>
       <c r="C79" s="163"/>
       <c r="D79" s="163"/>
@@ -76380,7 +76664,7 @@
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="165" t="s">
-        <v>4172</v>
+        <v>4180</v>
       </c>
       <c r="B81" s="171" t="s">
         <v>1140</v>
@@ -76432,7 +76716,7 @@
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="165" t="s">
-        <v>4173</v>
+        <v>4181</v>
       </c>
       <c r="B83" s="165" t="s">
         <v>3647</v>
@@ -76484,10 +76768,10 @@
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="165" t="s">
-        <v>4174</v>
+        <v>4182</v>
       </c>
       <c r="B85" s="165" t="s">
-        <v>4175</v>
+        <v>4183</v>
       </c>
       <c r="C85" s="163"/>
       <c r="D85" s="163"/>
@@ -76536,10 +76820,10 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="165" t="s">
-        <v>4176</v>
+        <v>4184</v>
       </c>
       <c r="B87" s="165" t="s">
-        <v>4106</v>
+        <v>4114</v>
       </c>
       <c r="C87" s="163"/>
       <c r="D87" s="163"/>
@@ -76588,10 +76872,10 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="165" t="s">
-        <v>4177</v>
+        <v>4185</v>
       </c>
       <c r="B89" s="165" t="s">
-        <v>4108</v>
+        <v>4116</v>
       </c>
       <c r="C89" s="163"/>
       <c r="D89" s="163"/>
@@ -76640,10 +76924,10 @@
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="165" t="s">
-        <v>4178</v>
+        <v>4186</v>
       </c>
       <c r="B91" s="165" t="s">
-        <v>4110</v>
+        <v>4118</v>
       </c>
       <c r="C91" s="163"/>
       <c r="D91" s="163"/>
